--- a/2sci_online.xlsx
+++ b/2sci_online.xlsx
@@ -15,55 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="35">
-  <si>
-    <t>ناجح ✓</t>
-  </si>
-  <si>
-    <t>2026-03-02 21:39</t>
-  </si>
-  <si>
-    <t>60.0%</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>01095106575</t>
-  </si>
-  <si>
-    <t>hanawalynono@gmail.com</t>
-  </si>
-  <si>
-    <t>هنا والي صالح</t>
-  </si>
-  <si>
-    <t>2026-03-03 12:51</t>
-  </si>
-  <si>
-    <t>01115527889</t>
-  </si>
-  <si>
-    <t>Lomasalma@icloud.com</t>
-  </si>
-  <si>
-    <t>سلمي اشرف عبدالحيم علي</t>
-  </si>
-  <si>
-    <t>2026-03-04 01:27</t>
-  </si>
-  <si>
-    <t>100.0%</t>
-  </si>
-  <si>
-    <t>01210081096</t>
-  </si>
-  <si>
-    <t>malaak.7assan100@gmail.com</t>
-  </si>
-  <si>
-    <t>Malak Hassan</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="19">
   <si>
     <t>الحالة</t>
   </si>
@@ -113,13 +65,13 @@
     <t>#</t>
   </si>
   <si>
-    <t>نتائج الامتحان: Quiz 3 Applied - 2nd Term - Online</t>
+    <t>نتائج الامتحان: Quiz 5 Applied - 2nd Term - Online</t>
   </si>
   <si>
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-04 19:31</t>
+    <t>تاريخ التصدير: 2026-03-13 19:30</t>
   </si>
 </sst>
 </file>
@@ -197,13 +149,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
@@ -507,7 +456,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -529,209 +478,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="3" t="s">
-        <v>32</v>
+      <c r="A1" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="3" t="s">
-        <v>33</v>
+      <c r="A2" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="3" t="s">
-        <v>34</v>
+      <c r="A3" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" s="2">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" s="2">
-        <v>2</v>
-      </c>
-      <c r="G5" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="H5" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="2">
-        <v>5</v>
-      </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2">
-        <v>5</v>
-      </c>
-      <c r="N5" s="2">
-        <v>16.5</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" s="2">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" s="2">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="H6" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J6" s="2">
-        <v>3</v>
-      </c>
-      <c r="K6" s="2">
-        <v>2</v>
-      </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2">
-        <v>5</v>
-      </c>
-      <c r="N6" s="2">
-        <v>8.23</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="A7" s="2">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="2">
-        <v>1</v>
-      </c>
-      <c r="G7" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J7" s="2">
-        <v>3</v>
-      </c>
-      <c r="K7" s="2">
-        <v>2</v>
-      </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2">
-        <v>5</v>
-      </c>
-      <c r="N7" s="2">
-        <v>10.45</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P7" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/2sci_online.xlsx
+++ b/2sci_online.xlsx
@@ -15,7 +15,43 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="31">
+  <si>
+    <t>ناجح ✓</t>
+  </si>
+  <si>
+    <t>2026-03-14 14:10</t>
+  </si>
+  <si>
+    <t>80.0%</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>01280132743</t>
+  </si>
+  <si>
+    <t>mohamedmos615@gmail.com</t>
+  </si>
+  <si>
+    <t>محمد مصطفى أحمد</t>
+  </si>
+  <si>
+    <t>2026-03-17 20:40</t>
+  </si>
+  <si>
+    <t>100.0%</t>
+  </si>
+  <si>
+    <t>01101238555</t>
+  </si>
+  <si>
+    <t>mo7ameda7med150@gmail.com</t>
+  </si>
+  <si>
+    <t>محمد احمد نبيل</t>
+  </si>
   <si>
     <t>الحالة</t>
   </si>
@@ -71,7 +107,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-13 19:30</t>
+    <t>تاريخ التصدير: 2026-03-18 19:25</t>
   </si>
 </sst>
 </file>
@@ -149,10 +185,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
@@ -456,7 +495,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -478,67 +517,161 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="2" t="s">
-        <v>16</v>
+      <c r="A1" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="2" t="s">
-        <v>17</v>
+      <c r="A2" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="2" t="s">
-        <v>18</v>
+      <c r="A3" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="2">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="E5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J5" s="2">
+        <v>5</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2">
+        <v>5</v>
+      </c>
+      <c r="N5" s="2">
+        <v>4.42</v>
+      </c>
+      <c r="O5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="P5" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="2">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="J6" s="2">
+        <v>4</v>
+      </c>
+      <c r="K6" s="2">
         <v>1</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="L6" s="2"/>
+      <c r="M6" s="2">
+        <v>5</v>
+      </c>
+      <c r="N6" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P6" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/2sci_online.xlsx
+++ b/2sci_online.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="35">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -53,6 +53,18 @@
     <t>محمد احمد نبيل</t>
   </si>
   <si>
+    <t>2026-03-18 20:11</t>
+  </si>
+  <si>
+    <t>01090635624</t>
+  </si>
+  <si>
+    <t>yasser1062008@gmail.com</t>
+  </si>
+  <si>
+    <t>Yasser Mohamed fayez</t>
+  </si>
+  <si>
     <t>الحالة</t>
   </si>
   <si>
@@ -107,7 +119,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-18 19:25</t>
+    <t>تاريخ التصدير: 2026-03-18 20:39</t>
   </si>
 </sst>
 </file>
@@ -495,7 +507,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -518,67 +530,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -586,13 +598,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
@@ -601,27 +613,29 @@
         <v>1</v>
       </c>
       <c r="G5" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H5" s="2">
         <v>10.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J5" s="2">
-        <v>5</v>
-      </c>
-      <c r="K5" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K5" s="2">
+        <v>1</v>
+      </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2">
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>4.42</v>
+        <v>8.55</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -632,13 +646,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
@@ -647,31 +661,77 @@
         <v>1</v>
       </c>
       <c r="G6" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H6" s="2">
         <v>10.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J6" s="2">
-        <v>4</v>
-      </c>
-      <c r="K6" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2">
         <v>5</v>
       </c>
       <c r="N6" s="2">
+        <v>4.42</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="2">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J7" s="2">
+        <v>4</v>
+      </c>
+      <c r="K7" s="2">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2">
+        <v>5</v>
+      </c>
+      <c r="N7" s="2">
         <v>4.3</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/2sci_online.xlsx
+++ b/2sci_online.xlsx
@@ -119,7 +119,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-18 20:39</t>
+    <t>تاريخ التصدير: 2026-03-18 21:18</t>
   </si>
 </sst>
 </file>

--- a/2sci_online.xlsx
+++ b/2sci_online.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="112">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -65,6 +65,237 @@
     <t>Yasser Mohamed fayez</t>
   </si>
   <si>
+    <t>2026-03-18 21:35</t>
+  </si>
+  <si>
+    <t>01017244083</t>
+  </si>
+  <si>
+    <t>albaraam357@gmail.com</t>
+  </si>
+  <si>
+    <t>Albaraamohamed</t>
+  </si>
+  <si>
+    <t>2026-03-19 15:24</t>
+  </si>
+  <si>
+    <t>60.0%</t>
+  </si>
+  <si>
+    <t>01150877750</t>
+  </si>
+  <si>
+    <t>lamyaelmasry2006@gmail.com</t>
+  </si>
+  <si>
+    <t>ياسين محمد كامل</t>
+  </si>
+  <si>
+    <t>2026-03-19 19:12</t>
+  </si>
+  <si>
+    <t>01014788879</t>
+  </si>
+  <si>
+    <t>roaamohammed1752009@gmailcom</t>
+  </si>
+  <si>
+    <t>Roaa Mohammed hemeida galal</t>
+  </si>
+  <si>
+    <t>2026-03-21 19:57</t>
+  </si>
+  <si>
+    <t>01013377375</t>
+  </si>
+  <si>
+    <t>btsfangirlforever6@gmail.com</t>
+  </si>
+  <si>
+    <t>حنين محمد محمود</t>
+  </si>
+  <si>
+    <t>2026-03-23 17:32</t>
+  </si>
+  <si>
+    <t>01149060505</t>
+  </si>
+  <si>
+    <t>yasminmahmoud3032010@gmail.com</t>
+  </si>
+  <si>
+    <t>ياسمين محمود محمد خلاف</t>
+  </si>
+  <si>
+    <t>2026-03-24 17:51</t>
+  </si>
+  <si>
+    <t>01023678107</t>
+  </si>
+  <si>
+    <t>malk1662008@gmail.com</t>
+  </si>
+  <si>
+    <t>Malak Ahmed Aboubakr</t>
+  </si>
+  <si>
+    <t>2026-03-24 23:27</t>
+  </si>
+  <si>
+    <t>01013657697</t>
+  </si>
+  <si>
+    <t>reemreda1022010@gmail.com</t>
+  </si>
+  <si>
+    <t>reem reda Mohamed</t>
+  </si>
+  <si>
+    <t>2026-03-25 01:05</t>
+  </si>
+  <si>
+    <t>01027709112</t>
+  </si>
+  <si>
+    <t>tasneemabdelnasser0@gmail.com</t>
+  </si>
+  <si>
+    <t>Tasneem abdelnasser</t>
+  </si>
+  <si>
+    <t>2026-03-25 20:25</t>
+  </si>
+  <si>
+    <t>01121973130</t>
+  </si>
+  <si>
+    <t>seifzarad50@gmail.com</t>
+  </si>
+  <si>
+    <t>سيف ابراهيم ابوالعنين</t>
+  </si>
+  <si>
+    <t>2026-03-26 23:20</t>
+  </si>
+  <si>
+    <t>01090829109</t>
+  </si>
+  <si>
+    <t>Mylittleponymm431@gmail.com</t>
+  </si>
+  <si>
+    <t>Mariam Mo3taz Mohamed</t>
+  </si>
+  <si>
+    <t>2026-03-27 19:29</t>
+  </si>
+  <si>
+    <t>01113765691</t>
+  </si>
+  <si>
+    <t>ahmed148mody@gmail.com</t>
+  </si>
+  <si>
+    <t>أحمد محمد أحمد سلمان</t>
+  </si>
+  <si>
+    <t>2026-03-27 22:38</t>
+  </si>
+  <si>
+    <t>01111750903</t>
+  </si>
+  <si>
+    <t>yassinsona778@gmail.com</t>
+  </si>
+  <si>
+    <t>ياسين محمد جميل</t>
+  </si>
+  <si>
+    <t>2026-03-28 12:13</t>
+  </si>
+  <si>
+    <t>01551501457</t>
+  </si>
+  <si>
+    <t>roaaahmed21080001@gmail.com</t>
+  </si>
+  <si>
+    <t>رؤى احمد حسين</t>
+  </si>
+  <si>
+    <t>2026-03-28 12:14</t>
+  </si>
+  <si>
+    <t>01148353989</t>
+  </si>
+  <si>
+    <t>janaamrmohamed2472009@gmail.com</t>
+  </si>
+  <si>
+    <t>Jana Amr</t>
+  </si>
+  <si>
+    <t>2026-03-28 14:30</t>
+  </si>
+  <si>
+    <t>01225663353</t>
+  </si>
+  <si>
+    <t>tonymichel3030@gmail.com</t>
+  </si>
+  <si>
+    <t>Tony michel alfy</t>
+  </si>
+  <si>
+    <t>2026-03-28 21:46</t>
+  </si>
+  <si>
+    <t>01229920604</t>
+  </si>
+  <si>
+    <t>hanyyyfadyyy9@gmail.com</t>
+  </si>
+  <si>
+    <t>فادي هاني مكرم</t>
+  </si>
+  <si>
+    <t>2026-03-28 22:16</t>
+  </si>
+  <si>
+    <t>01032808309</t>
+  </si>
+  <si>
+    <t>ahmedav200@gmail.com</t>
+  </si>
+  <si>
+    <t>احمد سامح حسين</t>
+  </si>
+  <si>
+    <t>2026-03-29 21:13</t>
+  </si>
+  <si>
+    <t>01012462274</t>
+  </si>
+  <si>
+    <t>Loujain1356@gmail.com</t>
+  </si>
+  <si>
+    <t>Loujain Osama elsayed</t>
+  </si>
+  <si>
+    <t>2026-03-31 21:00</t>
+  </si>
+  <si>
+    <t>01115527889</t>
+  </si>
+  <si>
+    <t>Lomasalma@icloud.com</t>
+  </si>
+  <si>
+    <t>سلمي اشرف عبدالحيم علي</t>
+  </si>
+  <si>
     <t>الحالة</t>
   </si>
   <si>
@@ -119,7 +350,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-18 21:18</t>
+    <t>تاريخ التصدير: 2026-04-03 16:45</t>
   </si>
 </sst>
 </file>
@@ -507,7 +738,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -530,67 +761,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>32</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>33</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>108</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>107</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>25</v>
+        <v>102</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>19</v>
+        <v>96</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>16</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -598,13 +829,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
@@ -632,10 +863,10 @@
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>8.55</v>
+        <v>4.37</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -646,13 +877,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
@@ -678,10 +909,10 @@
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>4.42</v>
+        <v>2.82</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>0</v>
@@ -692,13 +923,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>4</v>
+        <v>82</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
@@ -707,31 +938,915 @@
         <v>1</v>
       </c>
       <c r="G7" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H7" s="2">
         <v>10.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J7" s="2">
-        <v>4</v>
-      </c>
-      <c r="K7" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2">
         <v>5</v>
       </c>
       <c r="N7" s="2">
+        <v>3.55</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="2">
+        <v>4</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="2">
+        <v>5</v>
+      </c>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2">
+        <v>5</v>
+      </c>
+      <c r="N8" s="2">
+        <v>2.38</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="2">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H9" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="2">
+        <v>5</v>
+      </c>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2">
+        <v>5</v>
+      </c>
+      <c r="N9" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="2">
+        <v>6</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H10" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="2">
+        <v>5</v>
+      </c>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2">
+        <v>5</v>
+      </c>
+      <c r="N10" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="2">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="2">
+        <v>5</v>
+      </c>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2">
+        <v>5</v>
+      </c>
+      <c r="N11" s="2">
+        <v>13.95</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="2">
+        <v>8</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H12" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="2">
+        <v>5</v>
+      </c>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2">
+        <v>5</v>
+      </c>
+      <c r="N12" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="2">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H13" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="2">
+        <v>3</v>
+      </c>
+      <c r="K13" s="2">
+        <v>2</v>
+      </c>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2">
+        <v>5</v>
+      </c>
+      <c r="N13" s="2">
+        <v>3.73</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="2">
+        <v>10</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H14" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J14" s="2">
+        <v>4</v>
+      </c>
+      <c r="K14" s="2">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2">
+        <v>5</v>
+      </c>
+      <c r="N14" s="2">
+        <v>5.07</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="2">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H15" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="2">
+        <v>5</v>
+      </c>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2">
+        <v>5</v>
+      </c>
+      <c r="N15" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="2">
+        <v>12</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H16" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="2">
+        <v>5</v>
+      </c>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2">
+        <v>5</v>
+      </c>
+      <c r="N16" s="2">
+        <v>5.82</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="2">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H17" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="2">
+        <v>5</v>
+      </c>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2">
+        <v>5</v>
+      </c>
+      <c r="N17" s="2">
+        <v>4.57</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="2">
+        <v>14</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H18" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="2">
+        <v>5</v>
+      </c>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2">
+        <v>5</v>
+      </c>
+      <c r="N18" s="2">
+        <v>10.85</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="2">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H19" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="2">
+        <v>5</v>
+      </c>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2">
+        <v>5</v>
+      </c>
+      <c r="N19" s="2">
         <v>4.3</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P7" s="2" t="s">
+      <c r="O19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="2">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H20" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2">
+        <v>5</v>
+      </c>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2">
+        <v>5</v>
+      </c>
+      <c r="N20" s="2">
+        <v>7.37</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="2">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H21" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="2">
+        <v>5</v>
+      </c>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2">
+        <v>5</v>
+      </c>
+      <c r="N21" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" s="2">
+        <v>18</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H22" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" s="2">
+        <v>3</v>
+      </c>
+      <c r="K22" s="2">
+        <v>2</v>
+      </c>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2">
+        <v>5</v>
+      </c>
+      <c r="N22" s="2">
+        <v>4.87</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" s="2">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H23" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J23" s="2">
+        <v>4</v>
+      </c>
+      <c r="K23" s="2">
+        <v>1</v>
+      </c>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2">
+        <v>5</v>
+      </c>
+      <c r="N23" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" s="2">
+        <v>20</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H24" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J24" s="2">
+        <v>4</v>
+      </c>
+      <c r="K24" s="2">
+        <v>1</v>
+      </c>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2">
+        <v>5</v>
+      </c>
+      <c r="N24" s="2">
+        <v>8.55</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" s="2">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H25" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J25" s="2">
+        <v>5</v>
+      </c>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2">
+        <v>5</v>
+      </c>
+      <c r="N25" s="2">
+        <v>4.42</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" s="2">
+        <v>22</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H26" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J26" s="2">
+        <v>4</v>
+      </c>
+      <c r="K26" s="2">
+        <v>1</v>
+      </c>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2">
+        <v>5</v>
+      </c>
+      <c r="N26" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P26" s="2" t="s">
         <v>0</v>
       </c>
     </row>
